--- a/all_sim/det_gpt_pet.xlsx
+++ b/all_sim/det_gpt_pet.xlsx
@@ -331,16 +331,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.8" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="9" max="9" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.7936507936507936</v>
+        <v>0.8662131519274376</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.4136507936507937</v>
+        <v>0.6368253968253968</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.3669108669108669</v>
+        <v>0.5802808302808303</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.13293650793650794</v>
+        <v>0.41858093002459196</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.04663780663780663</v>
+        <v>0.39254967254967255</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.32482993197278914</v>
+        <v>0.5195578231292517</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.11918726434855466</v>
+        <v>0.4663732931912265</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.11918726434855466</v>
+        <v>0.4663732931912265</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.11918726434855466</v>
+        <v>0.4663732931912265</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.11918726434855466</v>
+        <v>0.4663732931912265</v>
       </c>
     </row>
     <row r="2">
@@ -393,28 +393,28 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8055555555555556</v>
       </c>
     </row>
     <row r="3">
@@ -436,22 +436,22 @@
         <v>1.0</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="4">
@@ -470,25 +470,25 @@
         <v>1.0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.9857831239020144</v>
+        <v>0.9928915619510073</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.9857831239020144</v>
+        <v>0.9928915619510073</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.9857831239020144</v>
+        <v>0.9928915619510073</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.9857831239020144</v>
+        <v>0.9928915619510073</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.9857831239020144</v>
+        <v>0.9928915619510073</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.9857831239020144</v>
+        <v>0.9928915619510073</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.9857831239020144</v>
+        <v>0.9928915619510073</v>
       </c>
     </row>
     <row r="5">
@@ -498,34 +498,34 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.29684062062004885</v>
+        <v>0.6380036436433577</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.29684062062004885</v>
+        <v>0.6380036436433577</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.29684062062004885</v>
+        <v>0.6380036436433577</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.29684062062004885</v>
+        <v>0.6380036436433577</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.29684062062004885</v>
+        <v>0.6380036436433577</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.29684062062004885</v>
+        <v>0.6380036436433577</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.29684062062004885</v>
+        <v>0.6380036436433577</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.24946831773241573</v>
+        <v>0.6142078430767342</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.24946831773241573</v>
+        <v>0.6142078430767342</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.24946831773241573</v>
+        <v>0.6142078430767342</v>
       </c>
     </row>
     <row r="6">
@@ -544,25 +544,25 @@
         <v>1.0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.7206959706959708</v>
+        <v>0.8603479853479854</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.5761072261072262</v>
+        <v>0.7880536130536131</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.5761072261072262</v>
+        <v>0.7880536130536131</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.5761072261072262</v>
+        <v>0.7880536130536131</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.5761072261072262</v>
+        <v>0.7880536130536131</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.5761072261072262</v>
+        <v>0.7880536130536131</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.5761072261072262</v>
+        <v>0.7880536130536131</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.49300838352468784</v>
+        <v>0.7073737569797353</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.3198903338509317</v>
+        <v>0.5785498180882565</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.3198903338509317</v>
+        <v>0.5785498180882565</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.3198903338509317</v>
+        <v>0.5785498180882565</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.3198903338509317</v>
+        <v>0.5785498180882565</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.5647812194706603</v>
+        <v>0.6886406097353301</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.39208942426333726</v>
+        <v>0.5218022878892443</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.41725533596837944</v>
+        <v>0.5798851530141299</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.41725533596837944</v>
+        <v>0.5798851530141299</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.41725533596837944</v>
+        <v>0.5798851530141299</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.3636363636363637</v>
+        <v>0.6671122994652406</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.3636363636363637</v>
+        <v>0.6349431818181819</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.3636363636363637</v>
+        <v>0.6349431818181819</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.3636363636363637</v>
+        <v>0.6349431818181819</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.3636363636363637</v>
+        <v>0.6349431818181819</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.3636363636363637</v>
+        <v>0.6349431818181819</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.3636363636363637</v>
+        <v>0.6349431818181819</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.6971460638127305</v>
+        <v>0.833867149553424</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.5351851851851851</v>
+        <v>0.7129050925925926</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.37777777777777777</v>
+        <v>0.6412698412698412</v>
       </c>
     </row>
     <row r="9">
@@ -652,28 +652,28 @@
         <v>1.0</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.4</v>
+        <v>0.6464285714285715</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5053571428571428</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.38490853658536583</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6617647058823529</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +683,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.7459325396825397</v>
+        <v>0.8729662698412699</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.7459325396825397</v>
+        <v>0.8729662698412699</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7029914529914529</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7029914529914529</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7029914529914529</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7029914529914529</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7029914529914529</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7029914529914529</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7029914529914529</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7029914529914529</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
     </row>
     <row r="12">
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.763265306122449</v>
+        <v>0.8306122448979592</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.763265306122449</v>
+        <v>0.8306122448979592</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.763265306122449</v>
+        <v>0.8306122448979592</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.763265306122449</v>
+        <v>0.8306122448979592</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.763265306122449</v>
+        <v>0.8306122448979592</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.763265306122449</v>
+        <v>0.8306122448979592</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.763265306122449</v>
+        <v>0.8306122448979592</v>
       </c>
     </row>
     <row r="13">

--- a/all_sim/det_gpt_pet.xlsx
+++ b/all_sim/det_gpt_pet.xlsx
@@ -331,16 +331,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.8" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.8662131519274376</v>
+        <v>0.7450599287333981</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.6368253968253968</v>
+        <v>0.3557396825396826</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.5802808302808303</v>
+        <v>0.2911991007229103</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.41858093002459196</v>
+        <v>0.09361725911021684</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.39254967254967255</v>
+        <v>0.034440226440226436</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.5195578231292517</v>
+        <v>0.23202137998056369</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.4663732931912265</v>
+        <v>0.09696590997848516</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.4663732931912265</v>
+        <v>0.09696590997848516</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.4663732931912265</v>
+        <v>0.09696590997848516</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.4663732931912265</v>
+        <v>0.09696590997848516</v>
       </c>
     </row>
     <row r="2">
@@ -393,28 +393,28 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6296296296296295</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6296296296296295</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6296296296296295</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6296296296296295</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6296296296296295</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6296296296296295</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6296296296296295</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6296296296296295</v>
       </c>
     </row>
     <row r="3">
@@ -436,22 +436,22 @@
         <v>1.0</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="4">
@@ -470,25 +470,25 @@
         <v>1.0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.9928915619510073</v>
+        <v>0.9857831239020144</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.9928915619510073</v>
+        <v>0.9857831239020144</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.9928915619510073</v>
+        <v>0.9857831239020144</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.9928915619510073</v>
+        <v>0.9857831239020144</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.9928915619510073</v>
+        <v>0.9857831239020144</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.9928915619510073</v>
+        <v>0.9857831239020144</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.9928915619510073</v>
+        <v>0.9857831239020144</v>
       </c>
     </row>
     <row r="5">
@@ -498,34 +498,34 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.6380036436433577</v>
+        <v>0.29065644102379784</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.6380036436433577</v>
+        <v>0.29065644102379784</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.6380036436433577</v>
+        <v>0.29065644102379784</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.6380036436433577</v>
+        <v>0.29065644102379784</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.6380036436433577</v>
+        <v>0.29065644102379784</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.6380036436433577</v>
+        <v>0.29065644102379784</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.6380036436433577</v>
+        <v>0.29065644102379784</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.6142078430767342</v>
+        <v>0.24421635314857543</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.6142078430767342</v>
+        <v>0.24421635314857543</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.6142078430767342</v>
+        <v>0.24421635314857543</v>
       </c>
     </row>
     <row r="6">
@@ -544,25 +544,25 @@
         <v>1.0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.8603479853479854</v>
+        <v>0.7206959706959708</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.7880536130536131</v>
+        <v>0.5761072261072262</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.7880536130536131</v>
+        <v>0.5761072261072262</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.7880536130536131</v>
+        <v>0.5761072261072262</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.7880536130536131</v>
+        <v>0.5761072261072262</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.7880536130536131</v>
+        <v>0.5761072261072262</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.7880536130536131</v>
+        <v>0.5761072261072262</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.7073737569797353</v>
+        <v>0.45442511872710356</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.5785498180882565</v>
+        <v>0.2678151632240358</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.5785498180882565</v>
+        <v>0.2678151632240358</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.5785498180882565</v>
+        <v>0.2678151632240358</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.5785498180882565</v>
+        <v>0.2678151632240358</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.6886406097353301</v>
+        <v>0.4588847408199115</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.5218022878892443</v>
+        <v>0.2554522006564167</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.5798851530141299</v>
+        <v>0.3098183332938866</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.5798851530141299</v>
+        <v>0.3098183332938866</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.5798851530141299</v>
+        <v>0.3098183332938866</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.6671122994652406</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.6349431818181819</v>
+        <v>0.3295454545454546</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.6349431818181819</v>
+        <v>0.3295454545454546</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.6349431818181819</v>
+        <v>0.3295454545454546</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.6349431818181819</v>
+        <v>0.3295454545454546</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.6349431818181819</v>
+        <v>0.3295454545454546</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.6349431818181819</v>
+        <v>0.3295454545454546</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.833867149553424</v>
+        <v>0.6766417678182384</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.7129050925925926</v>
+        <v>0.47664930555555546</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.6412698412698412</v>
+        <v>0.34179894179894177</v>
       </c>
     </row>
     <row r="9">
@@ -652,28 +652,28 @@
         <v>1.0</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.6464285714285715</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.5053571428571428</v>
+        <v>0.20714285714285713</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.38490853658536583</v>
+        <v>0.04420731707317073</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.6617647058823529</v>
+        <v>0.4117647058823529</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +683,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.8729662698412699</v>
+        <v>0.7459325396825397</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.8729662698412699</v>
+        <v>0.7459325396825397</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.7029914529914529</v>
+        <v>0.42735042735042733</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.7029914529914529</v>
+        <v>0.42735042735042733</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.7029914529914529</v>
+        <v>0.42735042735042733</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.7029914529914529</v>
+        <v>0.42735042735042733</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.7029914529914529</v>
+        <v>0.42735042735042733</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.7029914529914529</v>
+        <v>0.42735042735042733</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.7029914529914529</v>
+        <v>0.42735042735042733</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.7029914529914529</v>
+        <v>0.42735042735042733</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
     </row>
     <row r="12">
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.8306122448979592</v>
+        <v>0.6853810912119951</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.8306122448979592</v>
+        <v>0.6853810912119951</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.8306122448979592</v>
+        <v>0.6853810912119951</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.8306122448979592</v>
+        <v>0.6853810912119951</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.8306122448979592</v>
+        <v>0.6853810912119951</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.8306122448979592</v>
+        <v>0.6853810912119951</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.8306122448979592</v>
+        <v>0.6853810912119951</v>
       </c>
     </row>
     <row r="13">
